--- a/Altium-library.xlsx
+++ b/Altium-library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400CC2AF-D89D-4091-8616-E06DFB12A0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1F7E14-AA87-4214-B925-ACC9CA81B37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Capacitors_General" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4037" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4051" uniqueCount="1464">
   <si>
     <t>Part Number</t>
   </si>
@@ -4438,6 +4438,15 @@
   </si>
   <si>
     <t>R0603_ERJ</t>
+  </si>
+  <si>
+    <t>600S101JW250X</t>
+  </si>
+  <si>
+    <t>100 pF ±5% 250V Ceramic Capacitor C0G, NP0 0603 (1608 Metric)</t>
+  </si>
+  <si>
+    <t>C-0603-600S101JW250X</t>
   </si>
 </sst>
 </file>
@@ -4587,7 +4596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4698,6 +4707,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5253,8 +5265,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="LibraryTable2" displayName="LibraryTable2" ref="A1:S16" totalsRowShown="0">
-  <autoFilter ref="A1:S16" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="LibraryTable2" displayName="LibraryTable2" ref="A1:S17" totalsRowShown="0">
+  <autoFilter ref="A1:S17" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Part Number"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Description"/>
@@ -5627,2200 +5639,2200 @@
   <dimension ref="A1:O44"/>
   <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.25" style="39" customWidth="1"/>
-    <col min="2" max="2" width="66" style="39" customWidth="1"/>
-    <col min="3" max="3" width="24" style="39" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="39" customWidth="1"/>
-    <col min="5" max="5" width="7.625" style="39" customWidth="1"/>
-    <col min="6" max="6" width="11.125" style="39" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="39" customWidth="1"/>
-    <col min="8" max="8" width="10.75" style="39" customWidth="1"/>
-    <col min="9" max="9" width="9" style="39" customWidth="1"/>
-    <col min="10" max="10" width="24.875" style="39" customWidth="1"/>
-    <col min="11" max="11" width="16.875" style="39" customWidth="1"/>
-    <col min="12" max="12" width="26.375" style="39" customWidth="1"/>
-    <col min="13" max="13" width="14.75" style="39" customWidth="1"/>
-    <col min="14" max="14" width="26.375" style="39" customWidth="1"/>
-    <col min="15" max="15" width="34.25" style="39" customWidth="1"/>
-    <col min="16" max="16" width="22.5" style="39" customWidth="1"/>
-    <col min="17" max="17" width="23.5" style="39" customWidth="1"/>
-    <col min="18" max="16384" width="11.125" style="39"/>
+    <col min="1" max="1" width="44.25" style="40" customWidth="1"/>
+    <col min="2" max="2" width="66" style="40" customWidth="1"/>
+    <col min="3" max="3" width="24" style="40" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="40" customWidth="1"/>
+    <col min="5" max="5" width="7.625" style="40" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="40" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="40" customWidth="1"/>
+    <col min="8" max="8" width="10.75" style="40" customWidth="1"/>
+    <col min="9" max="9" width="9" style="40" customWidth="1"/>
+    <col min="10" max="10" width="24.875" style="40" customWidth="1"/>
+    <col min="11" max="11" width="16.875" style="40" customWidth="1"/>
+    <col min="12" max="12" width="26.375" style="40" customWidth="1"/>
+    <col min="13" max="13" width="14.75" style="40" customWidth="1"/>
+    <col min="14" max="14" width="26.375" style="40" customWidth="1"/>
+    <col min="15" max="15" width="34.25" style="40" customWidth="1"/>
+    <col min="16" max="16" width="22.5" style="40" customWidth="1"/>
+    <col min="17" max="17" width="23.5" style="40" customWidth="1"/>
+    <col min="18" max="16384" width="11.125" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="40" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="40">
         <v>50</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="39" t="str">
+      <c r="M2" s="40" t="str">
         <f t="shared" ref="M2:M43" si="0">"C"&amp;D2</f>
         <v>C0402</v>
       </c>
-      <c r="N2" s="39" t="str">
+      <c r="N2" s="40" t="str">
         <f>"C-"&amp;D2&amp;"-"&amp;G2&amp;"-"&amp;F2&amp;"-"&amp;E2&amp;" "&amp;IF(H2="±0,03","A",IF(H2="±0,1","B",IF(H2="±0,25","C",IF(H2="±0,5","D",IF(H2="±1%","F",IF(H2="±2%","G",IF(H2="±5%","J",IF(H2="±10%","K",IF(H2="±20%","M","")))))))))</f>
         <v>C-0402-NP0-50-0.01uF J</v>
       </c>
-      <c r="O2" s="39" t="str">
+      <c r="O2" s="40" t="str">
         <f t="shared" ref="O2:O41" si="1">N2</f>
         <v>C-0402-NP0-50-0.01uF J</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="40">
         <v>16</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="K3" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="39" t="s">
+      <c r="L3" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="39" t="str">
+      <c r="M3" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N3" s="39" t="str">
+      <c r="N3" s="40" t="str">
         <f>"C-"&amp;D3&amp;"-"&amp;G3&amp;"-"&amp;F3&amp;"-"&amp;E3&amp;" "&amp;IF(H3="±0,03","A",IF(H3="±0,1","B",IF(H3="±0,25","C",IF(H3="±0,5","D",IF(H3="±1%","F",IF(H3="±2%","G",IF(H3="±5%","J",IF(H3="±10%","K",IF(H3="±20%","M","")))))))))</f>
         <v>C-0402-X7R-16-0.068uF M</v>
       </c>
-      <c r="O3" s="39" t="str">
+      <c r="O3" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-16-0.068uF M</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="40" t="s">
         <v>1298</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="41">
         <v>16</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="39" t="s">
+      <c r="J4" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="39" t="s">
+      <c r="L4" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="39" t="str">
+      <c r="M4" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N4" s="39" t="str">
+      <c r="N4" s="40" t="str">
         <f>"C-"&amp;D4&amp;"-"&amp;G4&amp;"-"&amp;F4&amp;"-"&amp;E4&amp;" "&amp;IF(H4="±0,03","A",IF(H4="±0,1","B",IF(H4="±0,25","C",IF(H4="±0,5","D",IF(H4="±1%","F",IF(H4="±2%","G",IF(H4="±5%","J",IF(H4="±10%","K",IF(H4="±20%","M","")))))))))</f>
         <v>C-0402-X7R-16-0.1uF K</v>
       </c>
-      <c r="O4" s="39" t="str">
+      <c r="O4" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-16-0.1uF K</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="40">
         <v>50</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="39" t="s">
+      <c r="L5" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="39" t="str">
+      <c r="M5" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N5" s="39" t="str">
+      <c r="N5" s="40" t="str">
         <f>"C-"&amp;D5&amp;"-"&amp;G5&amp;"-"&amp;F5&amp;"-"&amp;E5&amp;" "&amp;IF(H5="±0,03","A",IF(H5="±0,1","B",IF(H5="±0,25","C",IF(H5="±0,5","D",IF(H5="±1%","F",IF(H5="±2%","G",IF(H5="±5%","J",IF(H5="±10%","K",IF(H5="±20%","M","")))))))))</f>
         <v>C-0402-X5R-50-0.1uF K</v>
       </c>
-      <c r="O5" s="39" t="str">
+      <c r="O5" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-50-0.1uF K</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="40">
         <v>16</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="39" t="s">
+      <c r="K6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="39" t="s">
+      <c r="L6" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="39" t="str">
+      <c r="M6" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N6" s="39" t="str">
+      <c r="N6" s="40" t="str">
         <f>"C-"&amp;D6&amp;"-"&amp;G6&amp;"-"&amp;F6&amp;"-"&amp;E6&amp;" "&amp;IF(H6="±0,03","A",IF(H6="±0,1","B",IF(H6="±0,25","C",IF(H6="±0,5","D",IF(H6="±1%","F",IF(H6="±2%","G",IF(H6="±5%","J",IF(H6="±10%","K",IF(H6="±20%","M","")))))))))</f>
         <v>C-0402-X5R-16-0.1uF K</v>
       </c>
-      <c r="O6" s="39" t="str">
+      <c r="O6" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-16-0.1uF K</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <v>16</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="39" t="s">
+      <c r="J7" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="39" t="s">
+      <c r="K7" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="39" t="s">
+      <c r="L7" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="39" t="str">
+      <c r="M7" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N7" s="39" t="str">
+      <c r="N7" s="40" t="str">
         <f>"C-"&amp;D7&amp;"-"&amp;G7&amp;"-"&amp;F7&amp;"-"&amp;E7&amp;" "&amp;IF(H7="±0,03","A",IF(H7="±0,1","B",IF(H7="±0,25","C",IF(H7="±0,5","D",IF(H7="±1%","F",IF(H7="±2%","G",IF(H7="±5%","J",IF(H7="±10%","K",IF(H7="±20%","M","")))))))))</f>
         <v>C-0402-X5R-16-0.22uF M</v>
       </c>
-      <c r="O7" s="39" t="str">
+      <c r="O7" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-16-0.22uF M</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="40">
         <v>2220</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="40">
         <v>50</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="39" t="s">
+      <c r="J8" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="39" t="s">
+      <c r="L8" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="39" t="str">
+      <c r="M8" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C2220</v>
       </c>
-      <c r="N8" s="39" t="str">
+      <c r="N8" s="40" t="str">
         <f>"C-"&amp;D8&amp;"-"&amp;G8&amp;"-"&amp;F8&amp;"-"&amp;E8&amp;" "&amp;IF(H8="±0,03","A",IF(H8="±0,1","B",IF(H8="±0,25","C",IF(H8="±0,5","D",IF(H8="±1%","F",IF(H8="±2%","G",IF(H8="±5%","J",IF(H8="±10%","K",IF(H8="±20%","M","")))))))))</f>
         <v>C-2220-NP0-50-0.47uF J</v>
       </c>
-      <c r="O8" s="39" t="str">
+      <c r="O8" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-2220-NP0-50-0.47uF J</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="40">
         <v>16</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="K9" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="39" t="str">
+      <c r="M9" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N9" s="39" t="str">
+      <c r="N9" s="40" t="str">
         <f>"C-"&amp;D9&amp;"-"&amp;G9&amp;"-"&amp;F9&amp;"-"&amp;E9&amp;" "&amp;IF(H9="±0,03","A",IF(H9="±0,1","B",IF(H9="±0,25","C",IF(H9="±0,5","D",IF(H9="±1%","F",IF(H9="±2%","G",IF(H9="±5%","J",IF(H9="±10%","K",IF(H9="±20%","M","")))))))))</f>
         <v>C-0402-X5R-16-0.47uF M</v>
       </c>
-      <c r="O9" s="39" t="str">
+      <c r="O9" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-16-0.47uF M</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="41">
         <v>50</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="39" t="s">
+      <c r="J10" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="39" t="s">
+      <c r="K10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="39" t="s">
+      <c r="L10" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="39" t="str">
+      <c r="M10" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N10" s="39" t="str">
+      <c r="N10" s="40" t="str">
         <f>"C-"&amp;D10&amp;"-"&amp;G10&amp;"-"&amp;F10&amp;"-"&amp;E10&amp;" "&amp;IF(H10="±0,03","A",IF(H10="±0,1","B",IF(H10="±0,25","C",IF(H10="±0,5","D",IF(H10="±1%","F",IF(H10="±2%","G",IF(H10="±5%","J",IF(H10="±10%","K",IF(H10="±20%","M","")))))))))</f>
         <v>C-0402-NP0-50-1000pF J</v>
       </c>
-      <c r="O10" s="39" t="str">
+      <c r="O10" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-NP0-50-1000pF J</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="40">
         <v>50</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I11" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="39" t="s">
+      <c r="K11" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="39" t="s">
+      <c r="L11" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="39" t="str">
+      <c r="M11" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N11" s="39" t="str">
+      <c r="N11" s="40" t="str">
         <f>"C-"&amp;D11&amp;"-"&amp;G11&amp;"-"&amp;F11&amp;"-"&amp;E11&amp;" "&amp;IF(H11="±0,03","A",IF(H11="±0,1","B",IF(H11="±0,25","C",IF(H11="±0,5","D",IF(H11="±1%","F",IF(H11="±2%","G",IF(H11="±5%","J",IF(H11="±10%","K",IF(H11="±20%","M","")))))))))</f>
         <v>C-0402-NP0-50-100pF G</v>
       </c>
-      <c r="O11" s="39" t="str">
+      <c r="O11" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-NP0-50-100pF G</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="40">
         <v>50</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="40" t="s">
+      <c r="H12" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="40" t="s">
+      <c r="I12" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="39" t="s">
+      <c r="J12" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="39" t="s">
+      <c r="K12" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L12" s="39" t="s">
+      <c r="L12" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M12" s="39" t="str">
+      <c r="M12" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N12" s="39" t="str">
+      <c r="N12" s="40" t="str">
         <f>"C-"&amp;D12&amp;"-"&amp;G12&amp;"-"&amp;F12&amp;"-"&amp;E12&amp;" "&amp;IF(H12="±0,03","A",IF(H12="±0,1","B",IF(H12="±0,25","C",IF(H12="±0,5","D",IF(H12="±1%","F",IF(H12="±2%","G",IF(H12="±5%","J",IF(H12="±10%","K",IF(H12="±20%","M","")))))))))</f>
         <v>C-0402-NP0-50-10pF J</v>
       </c>
-      <c r="O12" s="39" t="str">
+      <c r="O12" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-NP0-50-10pF J</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="40">
         <v>50</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="39" t="s">
+      <c r="K13" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L13" s="39" t="s">
+      <c r="L13" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M13" s="39" t="str">
+      <c r="M13" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0805</v>
       </c>
-      <c r="N13" s="39" t="str">
+      <c r="N13" s="40" t="str">
         <f>"C-"&amp;D13&amp;"-"&amp;G13&amp;"-"&amp;F13&amp;"-"&amp;E13&amp;" "&amp;IF(H13="±0,03","A",IF(H13="±0,1","B",IF(H13="±0,25","C",IF(H13="±0,5","D",IF(H13="±1%","F",IF(H13="±2%","G",IF(H13="±5%","J",IF(H13="±10%","K",IF(H13="±20%","M","")))))))))</f>
         <v>C-0805-X5R-50-10uF K</v>
       </c>
-      <c r="O13" s="39" t="str">
+      <c r="O13" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0805-X5R-50-10uF K</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="40">
         <v>1206</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="40">
         <v>10</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="41" t="s">
         <v>1299</v>
       </c>
-      <c r="J14" s="39" t="s">
+      <c r="J14" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="39" t="s">
+      <c r="K14" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="39" t="s">
+      <c r="L14" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="39" t="str">
+      <c r="M14" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C1206</v>
       </c>
-      <c r="N14" s="39" t="s">
+      <c r="N14" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="O14" s="39" t="str">
+      <c r="O14" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-A-10-10uF K</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="39" t="s">
+      <c r="J15" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="K15" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="39" t="s">
+      <c r="L15" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M15" s="39" t="str">
+      <c r="M15" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N15" s="39" t="str">
+      <c r="N15" s="40" t="str">
         <f>"C-"&amp;D15&amp;"-"&amp;G15&amp;"-"&amp;F15&amp;"-"&amp;E15&amp;" "&amp;IF(H15="±0,03","A",IF(H15="±0,1","B",IF(H15="±0,25","C",IF(H15="±0,5","D",IF(H15="±1%","F",IF(H15="±2%","G",IF(H15="±5%","J",IF(H15="±10%","K",IF(H15="±20%","M","")))))))))</f>
         <v>C-0402-X5R-6.3-10uF M</v>
       </c>
-      <c r="O15" s="39" t="str">
+      <c r="O15" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-6.3-10uF M</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="40">
         <v>50</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="39" t="s">
+      <c r="J16" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="39" t="s">
+      <c r="K16" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L16" s="39" t="s">
+      <c r="L16" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M16" s="39" t="str">
+      <c r="M16" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N16" s="39" t="str">
+      <c r="N16" s="40" t="str">
         <f>"C-"&amp;D16&amp;"-"&amp;G16&amp;"-"&amp;F16&amp;"-"&amp;E16&amp;" "&amp;IF(H16="±0,03","A",IF(H16="±0,1","B",IF(H16="±0,25","C",IF(H16="±0,5","D",IF(H16="±1%","F",IF(H16="±2%","G",IF(H16="±5%","J",IF(H16="±10%","K",IF(H16="±20%","M","")))))))))</f>
         <v>C-0402-X7R-50-1500pF J</v>
       </c>
-      <c r="O16" s="39" t="str">
+      <c r="O16" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-50-1500pF J</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="40">
         <v>25</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J17" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="39" t="s">
+      <c r="L17" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M17" s="39" t="str">
+      <c r="M17" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N17" s="39" t="str">
+      <c r="N17" s="40" t="str">
         <f>"C-"&amp;D17&amp;"-"&amp;G17&amp;"-"&amp;F17&amp;"-"&amp;E17&amp;" "&amp;IF(H17="±0,03","A",IF(H17="±0,1","B",IF(H17="±0,25","C",IF(H17="±0,5","D",IF(H17="±1%","F",IF(H17="±2%","G",IF(H17="±5%","J",IF(H17="±10%","K",IF(H17="±20%","M","")))))))))</f>
         <v>C-0402-X7R-25-1800pF K</v>
       </c>
-      <c r="O17" s="39" t="str">
+      <c r="O17" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-25-1800pF K</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="40">
         <v>25</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="40" t="s">
+      <c r="I18" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J18" s="39" t="s">
+      <c r="J18" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="39" t="s">
+      <c r="K18" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="39" t="s">
+      <c r="L18" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M18" s="39" t="str">
+      <c r="M18" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N18" s="39" t="str">
+      <c r="N18" s="40" t="str">
         <f>"C-"&amp;D18&amp;"-"&amp;G18&amp;"-"&amp;F18&amp;"-"&amp;E18&amp;" "&amp;IF(H18="±0,03","A",IF(H18="±0,1","B",IF(H18="±0,25","C",IF(H18="±0,5","D",IF(H18="±1%","F",IF(H18="±2%","G",IF(H18="±5%","J",IF(H18="±10%","K",IF(H18="±20%","M","")))))))))</f>
         <v>C-0402-X5R-25-1uF M</v>
       </c>
-      <c r="O18" s="39" t="str">
+      <c r="O18" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-25-1uF M</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="40">
         <v>50</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M19" s="39" t="str">
+      <c r="M19" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N19" s="39" t="str">
+      <c r="N19" s="40" t="str">
         <f>"C-"&amp;D19&amp;"-"&amp;G19&amp;"-"&amp;F19&amp;"-"&amp;E19&amp;" "&amp;IF(H19="±0,03","A",IF(H19="±0,1","B",IF(H19="±0,25","C",IF(H19="±0,5","D",IF(H19="±1%","F",IF(H19="±2%","G",IF(H19="±5%","J",IF(H19="±10%","K",IF(H19="±20%","M","")))))))))</f>
         <v>C-0402-X7R-50-2200pF K</v>
       </c>
-      <c r="O19" s="39" t="str">
+      <c r="O19" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-50-2200pF K</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="39">
+      <c r="F20" s="40">
         <v>50</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I20" s="39" t="s">
+      <c r="I20" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="39" t="s">
+      <c r="J20" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="39" t="s">
+      <c r="K20" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="L20" s="39" t="s">
+      <c r="L20" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M20" s="39" t="str">
+      <c r="M20" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C10x10</v>
       </c>
-      <c r="N20" s="40" t="s">
+      <c r="N20" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="O20" s="39" t="str">
+      <c r="O20" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-UUD1H221MNL1GS</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="40">
         <v>16</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="39" t="s">
+      <c r="J21" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L21" s="39" t="s">
+      <c r="L21" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M21" s="39" t="str">
+      <c r="M21" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0603</v>
       </c>
-      <c r="N21" s="39" t="str">
+      <c r="N21" s="40" t="str">
         <f t="shared" ref="N21:N26" si="2">"C-"&amp;D21&amp;"-"&amp;G21&amp;"-"&amp;F21&amp;"-"&amp;E21&amp;" "&amp;IF(H21="±0,03","A",IF(H21="±0,1","B",IF(H21="±0,25","C",IF(H21="±0,5","D",IF(H21="±1%","F",IF(H21="±2%","G",IF(H21="±5%","J",IF(H21="±10%","K",IF(H21="±20%","M","")))))))))</f>
         <v>C-0603-X5R-16-22uF M</v>
       </c>
-      <c r="O21" s="39" t="str">
+      <c r="O21" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0603-X5R-16-22uF M</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="40">
         <v>50</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J22" s="39" t="s">
+      <c r="J22" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="39" t="s">
+      <c r="K22" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L22" s="39" t="s">
+      <c r="L22" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M22" s="39" t="str">
+      <c r="M22" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N22" s="39" t="str">
+      <c r="N22" s="40" t="str">
         <f t="shared" si="2"/>
         <v>C-0402-X7R-50-3300pF K</v>
       </c>
-      <c r="O22" s="39" t="str">
+      <c r="O22" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-50-3300pF K</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="D23" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="39">
+      <c r="F23" s="40">
         <v>50</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="I23" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="39" t="s">
+      <c r="J23" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="39" t="s">
+      <c r="K23" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L23" s="39" t="s">
+      <c r="L23" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M23" s="39" t="str">
+      <c r="M23" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N23" s="39" t="str">
+      <c r="N23" s="40" t="str">
         <f t="shared" si="2"/>
         <v>C-0402-NP0-50-390pF J</v>
       </c>
-      <c r="O23" s="39" t="str">
+      <c r="O23" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-NP0-50-390pF J</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="40">
         <v>50</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J24" s="39" t="s">
+      <c r="J24" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="39" t="s">
+      <c r="K24" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L24" s="39" t="s">
+      <c r="L24" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M24" s="39" t="str">
+      <c r="M24" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N24" s="39" t="str">
+      <c r="N24" s="40" t="str">
         <f t="shared" si="2"/>
         <v>C-0402-NP0-50-39pF J</v>
       </c>
-      <c r="O24" s="39" t="str">
+      <c r="O24" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-NP0-50-39pF J</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="E25" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="40">
         <v>50</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H25" s="40" t="s">
+      <c r="H25" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="40" t="s">
+      <c r="I25" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J25" s="39" t="s">
+      <c r="J25" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="39" t="s">
+      <c r="K25" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L25" s="39" t="s">
+      <c r="L25" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="39" t="str">
+      <c r="M25" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N25" s="39" t="str">
+      <c r="N25" s="40" t="str">
         <f t="shared" si="2"/>
         <v>C-0402-X7R-50-4700pF K</v>
       </c>
-      <c r="O25" s="39" t="str">
+      <c r="O25" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-50-4700pF K</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="40" t="s">
+      <c r="E26" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="F26" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="40" t="s">
+      <c r="H26" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I26" s="40" t="s">
+      <c r="I26" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J26" s="39" t="s">
+      <c r="J26" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="39" t="s">
+      <c r="K26" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="39" t="s">
+      <c r="L26" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M26" s="39" t="str">
+      <c r="M26" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0603</v>
       </c>
-      <c r="N26" s="39" t="str">
+      <c r="N26" s="40" t="str">
         <f t="shared" si="2"/>
         <v>C-0603-X5R-6.3-47uF M</v>
       </c>
-      <c r="O26" s="39" t="str">
+      <c r="O26" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0603-X5R-6.3-47uF M</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="39" t="s">
+      <c r="D27" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="39" t="s">
+      <c r="E27" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="41">
         <v>35</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I27" s="39" t="s">
+      <c r="I27" s="40" t="s">
         <v>1390</v>
       </c>
-      <c r="J27" s="39" t="s">
+      <c r="J27" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="39" t="s">
+      <c r="K27" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="L27" s="39" t="s">
+      <c r="L27" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M27" s="39" t="str">
+      <c r="M27" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C6.3x7.7</v>
       </c>
-      <c r="N27" s="40" t="s">
+      <c r="N27" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="O27" s="39" t="str">
+      <c r="O27" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-UUD1V680MCL1GS</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D28" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="40" t="s">
+      <c r="E28" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="39">
+      <c r="F28" s="40">
         <v>50</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="G28" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H28" s="40" t="s">
+      <c r="H28" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="40" t="s">
+      <c r="I28" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J28" s="39" t="s">
+      <c r="J28" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="39" t="s">
+      <c r="K28" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L28" s="39" t="s">
+      <c r="L28" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M28" s="39" t="str">
+      <c r="M28" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N28" s="39" t="str">
+      <c r="N28" s="40" t="str">
         <f>"C-"&amp;D28&amp;"-"&amp;G28&amp;"-"&amp;F28&amp;"-"&amp;E28&amp;" "&amp;IF(H28="±0,03","A",IF(H28="±0,1","B",IF(H28="±0,25","C",IF(H28="±0,5","D",IF(H28="±1%","F",IF(H28="±2%","G",IF(H28="±5%","J",IF(H28="±10%","K",IF(H28="±20%","M","")))))))))</f>
         <v>C-0402-X7R-50-8200pF K</v>
       </c>
-      <c r="O28" s="39" t="str">
+      <c r="O28" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-50-8200pF K</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="40">
         <v>1206</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G29" s="40" t="s">
+      <c r="G29" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="40" t="s">
+      <c r="H29" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="40" t="s">
+      <c r="I29" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J29" s="39" t="s">
+      <c r="J29" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="39" t="s">
+      <c r="K29" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L29" s="39" t="s">
+      <c r="L29" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M29" s="39" t="str">
+      <c r="M29" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C1206</v>
       </c>
-      <c r="N29" s="39" t="str">
+      <c r="N29" s="40" t="str">
         <f>"C-"&amp;D29&amp;"-"&amp;G29&amp;"-"&amp;F29&amp;"-"&amp;E29&amp;" "&amp;IF(H29="±0,03","A",IF(H29="±0,1","B",IF(H29="±0,25","C",IF(H29="±0,5","D",IF(H29="±1%","F",IF(H29="±2%","G",IF(H29="±5%","J",IF(H29="±10%","K",IF(H29="±20%","M","")))))))))</f>
         <v>C-1206-X5R-6.3-100uF K</v>
       </c>
-      <c r="O29" s="39" t="str">
+      <c r="O29" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-1206-X5R-6.3-100uF K</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
+      <c r="A30" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="40">
         <v>1210</v>
       </c>
-      <c r="E30" s="40" t="s">
+      <c r="E30" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="40">
         <v>25</v>
       </c>
-      <c r="G30" s="40" t="s">
+      <c r="G30" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H30" s="40" t="s">
+      <c r="H30" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="40" t="s">
+      <c r="I30" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J30" s="39" t="s">
+      <c r="J30" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="39" t="s">
+      <c r="K30" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L30" s="39" t="s">
+      <c r="L30" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M30" s="39" t="str">
+      <c r="M30" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C1210</v>
       </c>
-      <c r="N30" s="39" t="str">
+      <c r="N30" s="40" t="str">
         <f>"C-"&amp;D30&amp;"-"&amp;G30&amp;"-"&amp;F30&amp;"-"&amp;E30&amp;" "&amp;IF(H30="±0,03","A",IF(H30="±0,1","B",IF(H30="±0,25","C",IF(H30="±0,5","D",IF(H30="±1%","F",IF(H30="±2%","G",IF(H30="±5%","J",IF(H30="±10%","K",IF(H30="±20%","M","")))))))))</f>
         <v>C-1210-X7R-25-22uF K</v>
       </c>
-      <c r="O30" s="39" t="str">
+      <c r="O30" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-1210-X7R-25-22uF K</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D31" s="39" t="s">
+      <c r="D31" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="E31" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="40">
         <v>50</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="G31" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="40" t="s">
+      <c r="H31" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="I31" s="40" t="s">
+      <c r="I31" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J31" s="39" t="s">
+      <c r="J31" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="39" t="s">
+      <c r="K31" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="39" t="s">
+      <c r="L31" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M31" s="39" t="str">
+      <c r="M31" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N31" s="39" t="s">
+      <c r="N31" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="O31" s="39" t="str">
+      <c r="O31" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-NP0-50-4.7pF B</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="D32" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="40" t="s">
+      <c r="E32" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="F32" s="39">
+      <c r="F32" s="40">
         <v>10</v>
       </c>
-      <c r="G32" s="40" t="s">
+      <c r="G32" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H32" s="40" t="s">
+      <c r="H32" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I32" s="40" t="s">
+      <c r="I32" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J32" s="39" t="s">
+      <c r="J32" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="39" t="s">
+      <c r="K32" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="39" t="s">
+      <c r="L32" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M32" s="39" t="str">
+      <c r="M32" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N32" s="39" t="str">
+      <c r="N32" s="40" t="str">
         <f t="shared" ref="N32:O43" si="3">"C-"&amp;D32&amp;"-"&amp;G32&amp;"-"&amp;F32&amp;"-"&amp;E32&amp;" "&amp;IF(H32="±0,03","A",IF(H32="±0,1","B",IF(H32="±0,25","C",IF(H32="±0,5","D",IF(H32="±1%","F",IF(H32="±2%","G",IF(H32="±5%","J",IF(H32="±10%","K",IF(H32="±20%","M","")))))))))</f>
         <v>C-0402-X5R-10-10uF M</v>
       </c>
-      <c r="O32" s="39" t="str">
+      <c r="O32" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-10-10uF M</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
+      <c r="A33" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D33" s="39" t="s">
+      <c r="D33" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="E33" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="39">
+      <c r="F33" s="40">
         <v>25</v>
       </c>
-      <c r="G33" s="40" t="s">
+      <c r="G33" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H33" s="40" t="s">
+      <c r="H33" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="40" t="s">
+      <c r="I33" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J33" s="39" t="s">
+      <c r="J33" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K33" s="39" t="s">
+      <c r="K33" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L33" s="39" t="s">
+      <c r="L33" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M33" s="39" t="str">
+      <c r="M33" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0201</v>
       </c>
-      <c r="N33" s="39" t="str">
+      <c r="N33" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0201-X5R-25-0.1uF K</v>
       </c>
-      <c r="O33" s="39" t="str">
+      <c r="O33" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0201-X5R-25-0.1uF K</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="39" t="s">
+      <c r="A34" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D34" s="39" t="s">
+      <c r="D34" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="40" t="s">
+      <c r="E34" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="39">
+      <c r="F34" s="40">
         <v>16</v>
       </c>
-      <c r="G34" s="40" t="s">
+      <c r="G34" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H34" s="40" t="s">
+      <c r="H34" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="40" t="s">
+      <c r="I34" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J34" s="39" t="s">
+      <c r="J34" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="39" t="s">
+      <c r="K34" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L34" s="39" t="s">
+      <c r="L34" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M34" s="39" t="str">
+      <c r="M34" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N34" s="39" t="str">
+      <c r="N34" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0402-X7R-16-0.022uF K</v>
       </c>
-      <c r="O34" s="39" t="str">
+      <c r="O34" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X7R-16-0.022uF K</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C35" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D35" s="39" t="s">
+      <c r="D35" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="40">
         <v>10</v>
       </c>
-      <c r="G35" s="40" t="s">
+      <c r="G35" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H35" s="40" t="s">
+      <c r="H35" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I35" s="40" t="s">
+      <c r="I35" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J35" s="39" t="s">
+      <c r="J35" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="39" t="s">
+      <c r="K35" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L35" s="39" t="s">
+      <c r="L35" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M35" s="39" t="str">
+      <c r="M35" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0201</v>
       </c>
-      <c r="N35" s="39" t="str">
+      <c r="N35" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0201-X5R-10-1uF M</v>
       </c>
-      <c r="O35" s="39" t="str">
+      <c r="O35" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0201-X5R-10-1uF M</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
+      <c r="A36" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D36" s="39" t="s">
+      <c r="D36" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="E36" s="41" t="s">
+      <c r="E36" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F36" s="42" t="s">
+      <c r="F36" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G36" s="40" t="s">
+      <c r="G36" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H36" s="40" t="s">
+      <c r="H36" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I36" s="40" t="s">
+      <c r="I36" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J36" s="39" t="s">
+      <c r="J36" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K36" s="39" t="s">
+      <c r="K36" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L36" s="39" t="s">
+      <c r="L36" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="39" t="str">
+      <c r="M36" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0201</v>
       </c>
-      <c r="N36" s="39" t="str">
+      <c r="N36" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0201-X5R-6.3-4.7uF M</v>
       </c>
-      <c r="O36" s="39" t="str">
+      <c r="O36" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0201-X5R-6.3-4.7uF M</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="39" t="s">
+      <c r="A37" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="41" t="s">
+      <c r="E37" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="40">
         <v>10</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="G37" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="40" t="s">
+      <c r="H37" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I37" s="40" t="s">
+      <c r="I37" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J37" s="39" t="s">
+      <c r="J37" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K37" s="39" t="s">
+      <c r="K37" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L37" s="39" t="s">
+      <c r="L37" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M37" s="39" t="str">
+      <c r="M37" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N37" s="39" t="str">
+      <c r="N37" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0402-X5R-10-4.7uF M</v>
       </c>
-      <c r="O37" s="39" t="str">
+      <c r="O37" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-X5R-10-4.7uF M</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="39" t="s">
+      <c r="A38" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="39">
+      <c r="F38" s="40">
         <v>50</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="40" t="s">
+      <c r="H38" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="40" t="s">
+      <c r="I38" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J38" s="39" t="s">
+      <c r="J38" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K38" s="39" t="s">
+      <c r="K38" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="39" t="s">
+      <c r="L38" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M38" s="39" t="str">
+      <c r="M38" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0603</v>
       </c>
-      <c r="N38" s="39" t="str">
+      <c r="N38" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0603-NP0-50-1800pF J</v>
       </c>
-      <c r="O38" s="39" t="str">
+      <c r="O38" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0603-NP0-50-1800pF J</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="39" t="s">
+      <c r="A39" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="D39" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="40" t="s">
+      <c r="E39" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="F39" s="39">
+      <c r="F39" s="40">
         <v>25</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="40" t="s">
+      <c r="H39" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I39" s="40" t="s">
+      <c r="I39" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J39" s="39" t="s">
+      <c r="J39" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K39" s="39" t="s">
+      <c r="K39" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="39" t="s">
+      <c r="L39" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M39" s="39" t="str">
+      <c r="M39" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0603</v>
       </c>
-      <c r="N39" s="39" t="str">
+      <c r="N39" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0603-NP0-25-0.012uF J</v>
       </c>
-      <c r="O39" s="39" t="str">
+      <c r="O39" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0603-NP0-25-0.012uF J</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="39" t="s">
+      <c r="A40" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D40" s="39">
+      <c r="D40" s="40">
         <v>1206</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="F40" s="39">
+      <c r="F40" s="40">
         <v>25</v>
       </c>
-      <c r="G40" s="40" t="s">
+      <c r="G40" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H40" s="40" t="s">
+      <c r="H40" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I40" s="40" t="s">
+      <c r="I40" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J40" s="39" t="s">
+      <c r="J40" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K40" s="39" t="s">
+      <c r="K40" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L40" s="39" t="s">
+      <c r="L40" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M40" s="39" t="str">
+      <c r="M40" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C1206</v>
       </c>
-      <c r="N40" s="39" t="str">
+      <c r="N40" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-1206-NP0-25-0.33uF J</v>
       </c>
-      <c r="O40" s="39" t="str">
+      <c r="O40" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-1206-NP0-25-0.33uF J</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="39" t="s">
+      <c r="A41" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="40" t="s">
+      <c r="C41" s="41" t="s">
         <v>630</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="40" t="s">
+      <c r="E41" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="F41" s="39">
+      <c r="F41" s="40">
         <v>50</v>
       </c>
-      <c r="G41" s="40" t="s">
+      <c r="G41" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H41" s="40" t="s">
+      <c r="H41" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="40" t="s">
+      <c r="I41" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="39" t="s">
+      <c r="J41" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="39" t="s">
+      <c r="K41" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L41" s="39" t="s">
+      <c r="L41" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M41" s="39" t="str">
+      <c r="M41" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0402</v>
       </c>
-      <c r="N41" s="39" t="str">
+      <c r="N41" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0402-NP0-50-130pF J</v>
       </c>
-      <c r="O41" s="39" t="str">
+      <c r="O41" s="40" t="str">
         <f t="shared" si="1"/>
         <v>C-0402-NP0-50-130pF J</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="39" t="s">
+      <c r="A42" s="40" t="s">
         <v>1386</v>
       </c>
-      <c r="B42" s="39" t="s">
+      <c r="B42" s="40" t="s">
         <v>1387</v>
       </c>
-      <c r="C42" s="40" t="s">
+      <c r="C42" s="41" t="s">
         <v>1377</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="40" t="s">
         <v>1388</v>
       </c>
-      <c r="E42" s="39" t="s">
+      <c r="E42" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="F42" s="39">
+      <c r="F42" s="40">
         <v>35</v>
       </c>
-      <c r="G42" s="39" t="s">
+      <c r="G42" s="40" t="s">
         <v>1389</v>
       </c>
-      <c r="H42" s="40" t="s">
+      <c r="H42" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I42" s="39" t="s">
+      <c r="I42" s="40" t="s">
         <v>1390</v>
       </c>
-      <c r="J42" s="39" t="s">
+      <c r="J42" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K42" s="39" t="s">
+      <c r="K42" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="L42" s="39" t="s">
+      <c r="L42" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M42" s="39" t="s">
+      <c r="M42" s="40" t="s">
         <v>1417</v>
       </c>
-      <c r="N42" s="39" t="s">
+      <c r="N42" s="40" t="s">
         <v>1391</v>
       </c>
-      <c r="O42" s="39" t="s">
+      <c r="O42" s="40" t="s">
         <v>1391</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="39" t="s">
+      <c r="A43" s="40" t="s">
         <v>1392</v>
       </c>
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="40" t="s">
         <v>1393</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="40" t="s">
         <v>630</v>
       </c>
-      <c r="D43" s="43" t="s">
+      <c r="D43" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="39" t="s">
+      <c r="E43" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F43" s="39">
+      <c r="F43" s="40">
         <v>50</v>
       </c>
-      <c r="G43" s="44" t="s">
+      <c r="G43" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="40" t="s">
+      <c r="H43" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="40" t="s">
+      <c r="I43" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J43" s="39" t="s">
+      <c r="J43" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K43" s="39" t="s">
+      <c r="K43" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L43" s="39" t="s">
+      <c r="L43" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M43" s="39" t="str">
+      <c r="M43" s="40" t="str">
         <f t="shared" si="0"/>
         <v>C0805</v>
       </c>
-      <c r="N43" s="39" t="str">
+      <c r="N43" s="40" t="str">
         <f t="shared" si="3"/>
         <v>C-0805-X5R-50-10uF K</v>
       </c>
-      <c r="O43" s="39" t="str">
+      <c r="O43" s="40" t="str">
         <f>N43</f>
         <v>C-0805-X5R-50-10uF K</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="39" t="s">
+      <c r="A44" s="40" t="s">
         <v>1394</v>
       </c>
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="40" t="s">
         <v>1395</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="40" t="s">
         <v>630</v>
       </c>
-      <c r="D44" s="43" t="s">
+      <c r="D44" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="F44" s="39">
+      <c r="F44" s="40">
         <v>50</v>
       </c>
-      <c r="G44" s="40" t="s">
+      <c r="G44" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="H44" s="40" t="s">
+      <c r="H44" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="I44" s="40" t="s">
+      <c r="I44" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J44" s="39" t="s">
+      <c r="J44" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="39" t="s">
+      <c r="K44" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="L44" s="39" t="s">
+      <c r="L44" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="M44" s="39" t="str">
+      <c r="M44" s="40" t="str">
         <f t="shared" ref="M44" si="4">"C"&amp;D44</f>
         <v>C0805</v>
       </c>
-      <c r="N44" s="39" t="str">
+      <c r="N44" s="40" t="str">
         <f t="shared" ref="N44" si="5">"C-"&amp;D44&amp;"-"&amp;G44&amp;"-"&amp;F44&amp;"-"&amp;E44&amp;" "&amp;IF(H44="±0,03","A",IF(H44="±0,1","B",IF(H44="±0,25","C",IF(H44="±0,5","D",IF(H44="±1%","F",IF(H44="±2%","G",IF(H44="±5%","J",IF(H44="±10%","K",IF(H44="±20%","M","")))))))))</f>
         <v>C-0805-X7R-50-0.47uF M</v>
       </c>
-      <c r="O44" s="39" t="str">
+      <c r="O44" s="40" t="str">
         <f>N44</f>
         <v>C-0805-X7R-50-0.47uF M</v>
       </c>
@@ -13235,7 +13247,7 @@
         <v>26</v>
       </c>
       <c r="O3" s="5" t="str">
-        <f t="shared" ref="O3:O16" si="0">"C"&amp;D3</f>
+        <f t="shared" ref="O3:O17" si="0">"C"&amp;D3</f>
         <v>C0402</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -14046,11 +14058,69 @@
         <v>C-0402-NP0-50-22pF J</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="2">
+        <v>250</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>610</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>C0603</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="5" t="str">
+        <f t="shared" ref="Q17" si="4">O17&amp;"_RF"</f>
+        <v>C0603_RF</v>
+      </c>
+      <c r="R17" s="37" t="s">
+        <v>1463</v>
+      </c>
+      <c r="S17" s="5" t="str">
+        <f t="shared" ref="S17" si="5">R17</f>
+        <v>C-0603-600S101JW250X</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="containsBlanks" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17367,7 +17437,7 @@
       <c r="C81" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D81" s="45" t="s">
+      <c r="D81" s="46" t="s">
         <v>129</v>
       </c>
       <c r="E81" s="11" t="s">
@@ -18310,7 +18380,7 @@
       <c r="C104" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D104" s="45" t="s">
+      <c r="D104" s="46" t="s">
         <v>129</v>
       </c>
       <c r="E104" s="11" t="s">
@@ -18351,7 +18421,7 @@
       <c r="C105" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D105" s="45" t="s">
+      <c r="D105" s="46" t="s">
         <v>129</v>
       </c>
       <c r="E105" s="36" t="s">
@@ -18392,7 +18462,7 @@
       <c r="C106" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D106" s="45" t="s">
+      <c r="D106" s="46" t="s">
         <v>129</v>
       </c>
       <c r="E106" s="36" t="s">
@@ -18433,7 +18503,7 @@
       <c r="C107" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="D107" s="45" t="s">
+      <c r="D107" s="46" t="s">
         <v>129</v>
       </c>
       <c r="E107" s="36" t="s">
@@ -21450,7 +21520,7 @@
       <c r="E35" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="F35" s="46" t="s">
+      <c r="F35" s="47" t="s">
         <v>1163</v>
       </c>
       <c r="G35" s="5" t="s">

--- a/Altium-library.xlsx
+++ b/Altium-library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F8663A-4FF8-44EC-A16A-5810ADBCAE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2430F07-A356-4042-A4A5-DAED49A53D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Capacitors_General" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4434" uniqueCount="1608">
   <si>
     <t>Part Number</t>
   </si>
@@ -4208,9 +4208,6 @@
     <t>LM51581RTER</t>
   </si>
   <si>
-    <t>IC REG BOOST FLYBACK ADJ 16WQFN</t>
-  </si>
-  <si>
     <t>3.2 to 60</t>
   </si>
   <si>
@@ -4668,6 +4665,219 @@
   </si>
   <si>
     <t>±0.03</t>
+  </si>
+  <si>
+    <t>RC0402FR-07806RL</t>
+  </si>
+  <si>
+    <t>806Ω ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>806R</t>
+  </si>
+  <si>
+    <t>RC0402FR-07121KL</t>
+  </si>
+  <si>
+    <t>121kΩ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>121K</t>
+  </si>
+  <si>
+    <t>C3216X7S2A335M160AB</t>
+  </si>
+  <si>
+    <t>3.3 µF ±20% 100V Ceramic Capacitor X7S 1206 (3216 Metric)</t>
+  </si>
+  <si>
+    <t>3.3uF</t>
+  </si>
+  <si>
+    <t>X7S</t>
+  </si>
+  <si>
+    <t>C2012X7R2A104K125AA</t>
+  </si>
+  <si>
+    <t>0.1 µF ±10% 100V Ceramic Capacitor X7R 0805 (2012 Metric)</t>
+  </si>
+  <si>
+    <t>B82472G6223M000</t>
+  </si>
+  <si>
+    <t>FIXED IND 22UH 1.45A 91 MOHM SMD</t>
+  </si>
+  <si>
+    <t>7.3x7.3</t>
+  </si>
+  <si>
+    <t>22uH</t>
+  </si>
+  <si>
+    <t>TPS7A4001DGNR</t>
+  </si>
+  <si>
+    <t>IC REG LIN POS ADJ 50MA 8-HVSSOP</t>
+  </si>
+  <si>
+    <t>HVSSOP-8</t>
+  </si>
+  <si>
+    <t>7 to 100V</t>
+  </si>
+  <si>
+    <t>1.175 to 90</t>
+  </si>
+  <si>
+    <t>OPA197IDBV</t>
+  </si>
+  <si>
+    <t>Standard (General Purpose) Amplifier 1 Circuit Rail-to-Rail SOT-23-5</t>
+  </si>
+  <si>
+    <t>P-Channel 100 V 13A (Tc) 66W (Tc) Surface Mount TO-252AA (DPAK)</t>
+  </si>
+  <si>
+    <t>IRFR5410TRPBF</t>
+  </si>
+  <si>
+    <t>TO-252AA</t>
+  </si>
+  <si>
+    <t>2N7002DW</t>
+  </si>
+  <si>
+    <t>Mosfet Array 60V 115mA 200mW Surface Mount SC-88 (SC-70-6)</t>
+  </si>
+  <si>
+    <t>LM5158RTER</t>
+  </si>
+  <si>
+    <t>IC REG BOOST FLYBACK ADJ 16WQFN 3.2А</t>
+  </si>
+  <si>
+    <t>IC REG BOOST FLYBACK ADJ 16WQFN 1.62A</t>
+  </si>
+  <si>
+    <t>RC0402FR-07365KL</t>
+  </si>
+  <si>
+    <t>365kΩ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>365K</t>
+  </si>
+  <si>
+    <t>RC0402FR-0723K2L</t>
+  </si>
+  <si>
+    <t>23.2kΩ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>23K2</t>
+  </si>
+  <si>
+    <t>EEEFK2A330P</t>
+  </si>
+  <si>
+    <t>33uF</t>
+  </si>
+  <si>
+    <t>33 µF 100 V Aluminum Electrolytic Capacitors Radial, Can - SMD 2000 Hrs @ 105°C</t>
+  </si>
+  <si>
+    <t>C-EEEFK2A330P</t>
+  </si>
+  <si>
+    <t>BSS123</t>
+  </si>
+  <si>
+    <t>N-Channel 100 V 170mA 350mW (Ta) Surface Mount SOT-23-3</t>
+  </si>
+  <si>
+    <t>RC1210FR-07150RL</t>
+  </si>
+  <si>
+    <t>150Ω ±1% 0.063W 1210 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>1210</t>
+  </si>
+  <si>
+    <t>150R</t>
+  </si>
+  <si>
+    <t>4700 pF ±10% 100V Ceramic Capacitor X7R 0805 (2012 Metric)</t>
+  </si>
+  <si>
+    <t>C0805C472K1RACTU</t>
+  </si>
+  <si>
+    <t>TPS3711DDC</t>
+  </si>
+  <si>
+    <t>Supervisor Open Drain or Open Collector 1 Channel SOT-23-THIN</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>1.8 to 36V</t>
+  </si>
+  <si>
+    <t>RC0402FR-07309KL</t>
+  </si>
+  <si>
+    <t>309kΩ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>309K</t>
+  </si>
+  <si>
+    <t>Diode 100 V 1A Surface Mount DO-214AC (SMA)</t>
+  </si>
+  <si>
+    <t>US1B-E3/5AT</t>
+  </si>
+  <si>
+    <t>RC0402FR-0722KL</t>
+  </si>
+  <si>
+    <t>22kΩ±1% 0.063W 0402 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>22K</t>
+  </si>
+  <si>
+    <t>RC0402FR-0728KL</t>
+  </si>
+  <si>
+    <t>28K</t>
+  </si>
+  <si>
+    <t>RC0805FR-0710RL</t>
+  </si>
+  <si>
+    <t>10Ω ±1% 0.125W 0805 Thick Film Chip Resistor</t>
+  </si>
+  <si>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>0603LS-102XJ</t>
+  </si>
+  <si>
+    <t>1 µH Unshielded Inductor 400 mA 810mOhm Max 0603 (1608 Metric)</t>
+  </si>
+  <si>
+    <t>1000nH</t>
+  </si>
+  <si>
+    <t>15 @ 7.9MHz</t>
+  </si>
+  <si>
+    <t>0603LS</t>
   </si>
 </sst>
 </file>
@@ -4826,7 +5036,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4971,107 +5181,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="44">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -5327,6 +5445,101 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -5409,24 +5622,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LibraryTable1" displayName="LibraryTable1" ref="A1:O44" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
-  <autoFilter ref="A1:O44" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LibraryTable1" displayName="LibraryTable1" ref="A1:O48" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O48" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Part Number" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Description" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Manufacturer" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Package" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Value" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Voltage_V" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Dielectric_Class" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Tolerance" dataDxfId="34"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Type" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Library Path" dataDxfId="32"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Library Ref" dataDxfId="31"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Footprint Path 1" dataDxfId="30"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Footprint Ref 1" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="UID" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="PnP_name" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Part Number" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Description" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Manufacturer" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Package" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Value" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Voltage_V" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Dielectric_Class" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Tolerance" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Type" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Library Path" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Library Ref" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Footprint Path 1" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Footprint Ref 1" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="UID" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="PnP_name" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5437,7 +5650,7 @@
   <autoFilter ref="A1:K85" xr:uid="{00000000-0009-0000-0100-000012000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Part Number"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Description" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Description" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Manufacturer"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Package"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Type"/>
@@ -5473,19 +5686,17 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="LibraryTable10" displayName="LibraryTable10" ref="A1:L5" totalsRowShown="0">
-  <autoFilter ref="A1:L5" xr:uid="{00000000-0009-0000-0100-000014000000}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="LibraryTable10" displayName="LibraryTable10" ref="A1:J8" totalsRowShown="0">
+  <autoFilter ref="A1:J8" xr:uid="{00000000-0009-0000-0100-000014000000}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Part Number"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Description"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Manufacturer"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="Type"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="Library Path"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="Library Ref"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="Footprint Path 1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="Footprint Ref 1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="Footprint Path 2"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="Footprint Ref 2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="Footprint Path"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="Footprint Ref"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="UID"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="PnP_name"/>
   </tableColumns>
@@ -5494,23 +5705,23 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0BC0CEB-9F2A-4B60-80CC-73E86CD670F7}" name="LibraryTable102" displayName="LibraryTable102" ref="A1:J6" totalsRowShown="0" dataDxfId="10">
-  <autoFilter ref="A1:J6" xr:uid="{C0BC0CEB-9F2A-4B60-80CC-73E86CD670F7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0BC0CEB-9F2A-4B60-80CC-73E86CD670F7}" name="LibraryTable102" displayName="LibraryTable102" ref="A1:J7" totalsRowShown="0" dataDxfId="27">
+  <autoFilter ref="A1:J7" xr:uid="{C0BC0CEB-9F2A-4B60-80CC-73E86CD670F7}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{CB3A1C79-1A89-482A-98FF-C41ABF55BEEF}" name="Part Number" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{44955057-24B9-49CA-BBD9-66BEA7AAD0A1}" name="Description" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{A6EE2855-F91F-40CE-97EC-03EB26F3DEBD}" name="Manufacturer" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{7EBED3ED-A740-4E42-9A05-CF88E1F3F017}" name="Package" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{47F69D43-3545-427E-9423-0D1EAE321315}" name="Library Path" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{7AE79ED0-6335-4BAC-A922-B72C1B1C6B96}" name="Library Ref" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{5ADB13E3-D81C-41FE-BA7D-F7CC76008BC2}" name="Footprint Path" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{B53961E2-3E9A-4B9B-8A12-F92593621168}" name="Footprint Ref" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{CB3A1C79-1A89-482A-98FF-C41ABF55BEEF}" name="Part Number" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{44955057-24B9-49CA-BBD9-66BEA7AAD0A1}" name="Description" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{A6EE2855-F91F-40CE-97EC-03EB26F3DEBD}" name="Manufacturer" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{7EBED3ED-A740-4E42-9A05-CF88E1F3F017}" name="Package" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{47F69D43-3545-427E-9423-0D1EAE321315}" name="Library Path" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{7AE79ED0-6335-4BAC-A922-B72C1B1C6B96}" name="Library Ref" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{5ADB13E3-D81C-41FE-BA7D-F7CC76008BC2}" name="Footprint Path" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{B53961E2-3E9A-4B9B-8A12-F92593621168}" name="Footprint Ref" dataDxfId="19">
       <calculatedColumnFormula>#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8E7170F8-5D10-4576-8C4F-B02094A89A9D}" name="UID" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{8E7170F8-5D10-4576-8C4F-B02094A89A9D}" name="UID" dataDxfId="18">
       <calculatedColumnFormula>"D-"&amp;A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8C1DF0AF-C246-4EB5-9593-108B0C427AFA}" name="PnP_name" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{8C1DF0AF-C246-4EB5-9593-108B0C427AFA}" name="PnP_name" dataDxfId="17">
       <calculatedColumnFormula>I2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5585,8 +5796,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="LibraryTable4" displayName="LibraryTable4" ref="A1:L108" totalsRowShown="0">
-  <autoFilter ref="A1:L108" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="LibraryTable4" displayName="LibraryTable4" ref="A1:L117" totalsRowShown="0">
+  <autoFilter ref="A1:L117" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L103">
     <sortCondition ref="E1:E103"/>
   </sortState>
@@ -5609,8 +5820,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="LibraryTable5" displayName="LibraryTable5" ref="A1:M21" totalsRowShown="0">
-  <autoFilter ref="A1:M21" xr:uid="{00000000-0009-0000-0100-00000F000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="LibraryTable5" displayName="LibraryTable5" ref="A1:M22" totalsRowShown="0">
+  <autoFilter ref="A1:M22" xr:uid="{00000000-0009-0000-0100-00000F000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Part Number"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Description"/>
@@ -5631,8 +5842,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="LibraryTable6" displayName="LibraryTable6" ref="A1:K16" totalsRowShown="0">
-  <autoFilter ref="A1:K16" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="LibraryTable6" displayName="LibraryTable6" ref="A1:K17" totalsRowShown="0">
+  <autoFilter ref="A1:K17" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Part Number"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Description"/>
@@ -5669,30 +5880,30 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="LibraryTable3" displayName="LibraryTable3" ref="A1:M38" totalsRowShown="0" dataDxfId="24">
-  <autoFilter ref="A1:M38" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="LibraryTable3" displayName="LibraryTable3" ref="A1:M40" totalsRowShown="0" dataDxfId="43">
+  <autoFilter ref="A1:M40" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Part Number" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Description" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Manufacturer" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Package" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Vin" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Vout" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Type" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Library Path" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Library Ref" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Footprint Path" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Footprint Ref" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="UID" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="PnP_Name" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Part Number" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Description" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Manufacturer" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Package" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Vin" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Vout" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Type" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Library Path" dataDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Library Ref" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Footprint Path" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Footprint Ref" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="UID" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="PnP_Name" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="LibraryTable12" displayName="LibraryTable12" ref="A1:K14" totalsRowShown="0">
-  <autoFilter ref="A1:K14" xr:uid="{00000000-0009-0000-0100-000016000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="LibraryTable12" displayName="LibraryTable12" ref="A1:K15" totalsRowShown="0">
+  <autoFilter ref="A1:K15" xr:uid="{00000000-0009-0000-0100-000016000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="Part Number"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="Description"/>
@@ -5725,7 +5936,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="Library Path"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0C00-000007000000}" name="Library Ref"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0C00-000008000000}" name="Footprint Path"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0C00-000009000000}" name="Footprint Ref" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0C00-000009000000}" name="Footprint Ref" dataDxfId="29"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0C00-00000A000000}" name="UID"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0C00-00000B000000}" name="PnP_Name"/>
   </tableColumns>
@@ -5928,7 +6139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.25" style="36" customWidth="1"/>
@@ -6617,6 +6828,9 @@
       <c r="F14" s="36">
         <v>10</v>
       </c>
+      <c r="G14" s="36" t="s">
+        <v>1292</v>
+      </c>
       <c r="I14" s="37" t="s">
         <v>1211</v>
       </c>
@@ -6910,6 +7124,9 @@
       <c r="F20" s="36">
         <v>50</v>
       </c>
+      <c r="G20" s="36" t="s">
+        <v>1292</v>
+      </c>
       <c r="H20" s="37" t="s">
         <v>31</v>
       </c>
@@ -7256,6 +7473,9 @@
       <c r="F27" s="37">
         <v>35</v>
       </c>
+      <c r="G27" s="36" t="s">
+        <v>1292</v>
+      </c>
       <c r="H27" s="37" t="s">
         <v>31</v>
       </c>
@@ -8117,11 +8337,11 @@
         <v>26</v>
       </c>
       <c r="M44" s="36" t="str">
-        <f t="shared" ref="M44" si="5">"C"&amp;D44</f>
+        <f t="shared" ref="M44:M48" si="5">"C"&amp;D44</f>
         <v>C0805</v>
       </c>
       <c r="N44" s="36" t="str">
-        <f t="shared" ref="N44" si="6">"C-"&amp;D44&amp;"-"&amp;G44&amp;"-"&amp;F44&amp;"-"&amp;E44&amp;" "&amp;IF(H44="±0,03","A",IF(H44="±0,1","B",IF(H44="±0,25","C",IF(H44="±0,5","D",IF(H44="±1%","F",IF(H44="±2%","G",IF(H44="±5%","J",IF(H44="±10%","K",IF(H44="±20%","M","")))))))))</f>
+        <f>"C-"&amp;D44&amp;"-"&amp;G44&amp;"-"&amp;F44&amp;"-"&amp;E44&amp;" "&amp;IF(H44="±0,03","A",IF(H44="±0,1","B",IF(H44="±0,25","C",IF(H44="±0,5","D",IF(H44="±1%","F",IF(H44="±2%","G",IF(H44="±5%","J",IF(H44="±10%","K",IF(H44="±20%","M","")))))))))</f>
         <v>C-0805-X7R-50-0.47uF M</v>
       </c>
       <c r="O44" s="36" t="str">
@@ -8129,8 +8349,206 @@
         <v>C-0805-X7R-50-0.47uF M</v>
       </c>
     </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="36" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D45" s="36">
+        <v>1206</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F45" s="36">
+        <v>100</v>
+      </c>
+      <c r="G45" s="37" t="s">
+        <v>1546</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L45" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>C1206</v>
+      </c>
+      <c r="N45" s="36" t="str">
+        <f>"C-"&amp;D45&amp;"-"&amp;G45&amp;"-"&amp;F45&amp;"-"&amp;E45&amp;" "&amp;IF(H45="±0,03","A",IF(H45="±0,1","B",IF(H45="±0,25","C",IF(H45="±0,5","D",IF(H45="±1%","F",IF(H45="±2%","G",IF(H45="±5%","J",IF(H45="±10%","K",IF(H45="±20%","M","")))))))))</f>
+        <v>C-1206-X7S-100-3.3uF M</v>
+      </c>
+      <c r="O45" s="36" t="str">
+        <f>N45</f>
+        <v>C-1206-X7S-100-3.3uF M</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="36" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="36">
+        <v>100</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>C0805</v>
+      </c>
+      <c r="N46" s="36" t="str">
+        <f>"C-"&amp;D46&amp;"-"&amp;G46&amp;"-"&amp;F46&amp;"-"&amp;E46&amp;" "&amp;IF(H46="±0,03","A",IF(H46="±0,1","B",IF(H46="±0,25","C",IF(H46="±0,5","D",IF(H46="±1%","F",IF(H46="±2%","G",IF(H46="±5%","J",IF(H46="±10%","K",IF(H46="±20%","M","")))))))))</f>
+        <v>C-0805-X7R-100-0.1uF K</v>
+      </c>
+      <c r="O46" s="36" t="str">
+        <f>N46</f>
+        <v>C-0805-X7R-100-0.1uF K</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="36" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F47" s="36">
+        <v>100</v>
+      </c>
+      <c r="G47" s="36" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H47" s="50">
+        <v>0.2</v>
+      </c>
+      <c r="I47" s="36" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J47" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="L47" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>C10x10</v>
+      </c>
+      <c r="N47" s="36" t="s">
+        <v>1577</v>
+      </c>
+      <c r="O47" s="36" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="36" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" s="36">
+        <v>100</v>
+      </c>
+      <c r="G48" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="I48" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>C0805</v>
+      </c>
+      <c r="N48" s="36" t="str">
+        <f>"C-"&amp;D48&amp;"-"&amp;G48&amp;"-"&amp;F48&amp;"-"&amp;E48&amp;" "&amp;IF(H48="±0,03","A",IF(H48="±0,1","B",IF(H48="±0,25","C",IF(H48="±0,5","D",IF(H48="±1%","F",IF(H48="±2%","G",IF(H48="±5%","J",IF(H48="±10%","K",IF(H48="±20%","M","")))))))))</f>
+        <v>C-0805-X7R-100-4700pF K</v>
+      </c>
+      <c r="O48" s="36" t="str">
+        <f>N48</f>
+        <v>C-0805-X7R-100-4700pF K</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M44">
+  <conditionalFormatting sqref="M2:M48">
     <cfRule type="containsBlanks" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8201,7 +8619,7 @@
         <v>699</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>700</v>
@@ -8238,7 +8656,7 @@
         <v>704</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>700</v>
@@ -8275,7 +8693,7 @@
         <v>706</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>700</v>
@@ -8457,7 +8875,7 @@
         <v>725</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>700</v>
@@ -8494,7 +8912,7 @@
         <v>728</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>160</v>
@@ -8605,7 +9023,7 @@
         <v>737</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>700</v>
@@ -8642,7 +9060,7 @@
         <v>739</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>700</v>
@@ -8679,7 +9097,7 @@
         <v>740</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>1247</v>
@@ -8716,7 +9134,7 @@
         <v>742</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>1247</v>
@@ -8753,7 +9171,7 @@
         <v>744</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>700</v>
@@ -8790,7 +9208,7 @@
         <v>747</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>700</v>
@@ -8827,7 +9245,7 @@
         <v>749</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>700</v>
@@ -8864,7 +9282,7 @@
         <v>750</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>700</v>
@@ -8901,7 +9319,7 @@
         <v>751</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>700</v>
@@ -8938,7 +9356,7 @@
         <v>753</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>700</v>
@@ -8975,7 +9393,7 @@
         <v>755</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>160</v>
@@ -9012,7 +9430,7 @@
         <v>757</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>700</v>
@@ -9049,7 +9467,7 @@
         <v>761</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>700</v>
@@ -9086,7 +9504,7 @@
         <v>762</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>700</v>
@@ -9123,7 +9541,7 @@
         <v>763</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>700</v>
@@ -9160,7 +9578,7 @@
         <v>764</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>700</v>
@@ -9271,7 +9689,7 @@
         <v>1248</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>774</v>
@@ -9308,7 +9726,7 @@
         <v>778</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>700</v>
@@ -9345,7 +9763,7 @@
         <v>781</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>700</v>
@@ -9382,7 +9800,7 @@
         <v>783</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>700</v>
@@ -9419,7 +9837,7 @@
         <v>786</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>700</v>
@@ -9456,7 +9874,7 @@
         <v>789</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>700</v>
@@ -9493,7 +9911,7 @@
         <v>791</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>700</v>
@@ -9530,7 +9948,7 @@
         <v>792</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>700</v>
@@ -9567,7 +9985,7 @@
         <v>795</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>700</v>
@@ -9604,7 +10022,7 @@
         <v>797</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>700</v>
@@ -9641,7 +10059,7 @@
         <v>1249</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>700</v>
@@ -9678,7 +10096,7 @@
         <v>798</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>700</v>
@@ -9715,7 +10133,7 @@
         <v>799</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>700</v>
@@ -9752,7 +10170,7 @@
         <v>800</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>700</v>
@@ -9789,7 +10207,7 @@
         <v>802</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>700</v>
@@ -9826,7 +10244,7 @@
         <v>804</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>700</v>
@@ -9863,7 +10281,7 @@
         <v>805</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>700</v>
@@ -9937,7 +10355,7 @@
         <v>812</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>700</v>
@@ -10011,7 +10429,7 @@
         <v>817</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>160</v>
@@ -10048,7 +10466,7 @@
         <v>823</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>160</v>
@@ -10085,7 +10503,7 @@
         <v>827</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>160</v>
@@ -10122,7 +10540,7 @@
         <v>829</v>
       </c>
       <c r="B54" s="45" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>160</v>
@@ -10159,7 +10577,7 @@
         <v>830</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>700</v>
@@ -10196,7 +10614,7 @@
         <v>831</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>160</v>
@@ -10233,7 +10651,7 @@
         <v>832</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>160</v>
@@ -10270,7 +10688,7 @@
         <v>833</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>774</v>
@@ -10307,7 +10725,7 @@
         <v>836</v>
       </c>
       <c r="B59" s="45" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>700</v>
@@ -10344,7 +10762,7 @@
         <v>838</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>700</v>
@@ -10381,7 +10799,7 @@
         <v>839</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>700</v>
@@ -10418,7 +10836,7 @@
         <v>840</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>700</v>
@@ -10455,7 +10873,7 @@
         <v>842</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>700</v>
@@ -10492,7 +10910,7 @@
         <v>844</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>700</v>
@@ -10529,7 +10947,7 @@
         <v>846</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>700</v>
@@ -10566,7 +10984,7 @@
         <v>848</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>700</v>
@@ -10603,7 +11021,7 @@
         <v>850</v>
       </c>
       <c r="B67" s="45" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>815</v>
@@ -10640,7 +11058,7 @@
         <v>852</v>
       </c>
       <c r="B68" s="45" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>160</v>
@@ -10714,7 +11132,7 @@
         <v>859</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>160</v>
@@ -10751,7 +11169,7 @@
         <v>865</v>
       </c>
       <c r="B71" s="45" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>160</v>
@@ -10788,7 +11206,7 @@
         <v>868</v>
       </c>
       <c r="B72" s="47" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>160</v>
@@ -10825,7 +11243,7 @@
         <v>871</v>
       </c>
       <c r="B73" s="45" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>872</v>
@@ -10862,7 +11280,7 @@
         <v>874</v>
       </c>
       <c r="B74" s="45" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>160</v>
@@ -10899,7 +11317,7 @@
         <v>877</v>
       </c>
       <c r="B75" s="45" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>160</v>
@@ -10936,7 +11354,7 @@
         <v>878</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>160</v>
@@ -10973,7 +11391,7 @@
         <v>882</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>198</v>
@@ -11010,7 +11428,7 @@
         <v>885</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>160</v>
@@ -11047,7 +11465,7 @@
         <v>891</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>160</v>
@@ -11121,7 +11539,7 @@
         <v>1253</v>
       </c>
       <c r="B81" s="45" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>700</v>
@@ -11158,7 +11576,7 @@
         <v>1256</v>
       </c>
       <c r="B82" s="45" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>160</v>
@@ -11269,7 +11687,7 @@
         <v>1372</v>
       </c>
       <c r="B85" s="45" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>1247</v>
@@ -12230,7 +12648,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.625" style="2" customWidth="1"/>
@@ -12241,14 +12659,12 @@
     <col min="6" max="6" width="20.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="34.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="16.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.875" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="13" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.875" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -12268,25 +12684,19 @@
         <v>10</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L1" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>984</v>
       </c>
@@ -12311,16 +12721,16 @@
       <c r="H2" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="K2" s="2" t="str">
+      <c r="I2" s="2" t="str">
         <f>"Q-"&amp;F2</f>
         <v>Q-Si4101DY</v>
       </c>
-      <c r="L2" s="2" t="str">
-        <f>K2</f>
+      <c r="J2" s="2" t="str">
+        <f>I2</f>
         <v>Q-Si4101DY</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>991</v>
       </c>
@@ -12345,16 +12755,16 @@
       <c r="H3" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="K3" s="2" t="str">
+      <c r="I3" s="2" t="str">
         <f>"Q-"&amp;F3</f>
         <v>Q-BC817</v>
       </c>
-      <c r="L3" s="2" t="str">
-        <f>K3</f>
+      <c r="J3" s="2" t="str">
+        <f>I3</f>
         <v>Q-BC817</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>995</v>
       </c>
@@ -12379,16 +12789,16 @@
       <c r="H4" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="K4" s="2" t="str">
+      <c r="I4" s="2" t="str">
         <f>"Q-"&amp;F4</f>
         <v>Q-IRLML2060TRPBF</v>
       </c>
-      <c r="L4" s="2" t="str">
-        <f>K4</f>
+      <c r="J4" s="2" t="str">
+        <f>I4</f>
         <v>Q-IRLML2060TRPBF</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>999</v>
       </c>
@@ -12410,17 +12820,119 @@
       <c r="G5" s="10" t="s">
         <v>989</v>
       </c>
-      <c r="K5" s="2" t="str">
+      <c r="I5" s="2" t="str">
         <f>"Q-"&amp;F5</f>
         <v>Q-Si7232DN</v>
       </c>
-      <c r="L5" s="2" t="str">
-        <f>K5</f>
+      <c r="J5" s="2" t="str">
+        <f>I5</f>
         <v>Q-Si7232DN</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="I6" s="5" t="str">
+        <f>"Q-"&amp;F6</f>
+        <v>Q-IRFR5410TRPBF</v>
+      </c>
+      <c r="J6" s="5" t="str">
+        <f>I6</f>
+        <v>Q-IRFR5410TRPBF</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I7" s="5" t="str">
+        <f>"Q-"&amp;F7</f>
+        <v>Q-2N7002DW</v>
+      </c>
+      <c r="J7" s="5" t="str">
+        <f>I7</f>
+        <v>Q-2N7002DW</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="I8" s="5" t="str">
+        <f>"Q-"&amp;F8</f>
+        <v>Q-BSS123</v>
+      </c>
+      <c r="J8" s="5" t="str">
+        <f>I8</f>
+        <v>Q-BSS123</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="containsBlanks" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12432,7 +12944,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DCBABBA-8FB1-4A06-9817-B7D736D6A608}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.375" customWidth="1"/>
@@ -12485,7 +12997,7 @@
         <v>1001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1003</v>
@@ -12519,7 +13031,7 @@
         <v>1008</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>1003</v>
@@ -12553,7 +13065,7 @@
         <v>1268</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>1270</v>
@@ -12618,16 +13130,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D6" s="44" t="s">
         <v>1499</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>1498</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>1500</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>1005</v>
@@ -12639,7 +13151,7 @@
         <v>1007</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="I6" s="11" t="str">
         <f>"D-"&amp;A6</f>
@@ -12650,8 +13162,45 @@
         <v>D-B3100-13-F</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>578</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I7" s="11" t="str">
+        <f>"D-"&amp;A7</f>
+        <v>D-US1B-E3/5AT</v>
+      </c>
+      <c r="J7" s="11" t="str">
+        <f>I7</f>
+        <v>D-US1B-E3/5AT</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H3">
+    <cfRule type="containsBlanks" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
     <cfRule type="containsBlanks" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13666,7 +14215,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" t="s">
@@ -13727,7 +14276,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" t="s">
@@ -13788,7 +14337,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" t="s">
@@ -14551,16 +15100,16 @@
         <v>1365</v>
       </c>
       <c r="S17" s="5" t="str">
-        <f t="shared" ref="S17" si="5">R17</f>
+        <f>R17</f>
         <v>C-0603-600S101JW250X</v>
       </c>
     </row>
     <row r="18" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>604</v>
@@ -14569,7 +15118,7 @@
         <v>60</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="F18" s="2">
         <v>250</v>
@@ -14617,10 +15166,10 @@
     </row>
     <row r="19" spans="1:19" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>1532</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1533</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>1214</v>
@@ -14629,7 +15178,7 @@
         <v>90</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="F19" s="2">
         <v>250</v>
@@ -14638,7 +15187,7 @@
         <v>21</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="J19" t="s">
         <v>586</v>
@@ -14656,22 +15205,22 @@
         <v>26</v>
       </c>
       <c r="O19" s="5" t="str">
-        <f t="shared" ref="O19" si="6">"C"&amp;D19</f>
+        <f t="shared" ref="O19" si="5">"C"&amp;D19</f>
         <v>C0603</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>26</v>
       </c>
       <c r="Q19" s="5" t="str">
-        <f t="shared" ref="Q19" si="7">O19&amp;"_RF"</f>
+        <f t="shared" ref="Q19" si="6">O19&amp;"_RF"</f>
         <v>C0603_RF</v>
       </c>
       <c r="R19" s="5" t="str">
-        <f t="shared" ref="R19" si="8">"C-"&amp;D19&amp;"-"&amp;G19&amp;"-"&amp;F19&amp;"-"&amp;E19&amp;" "&amp;IF(H19="±0,03","A",IF(H19="±0,1","B",IF(H19="±0,25","C",IF(H19="±0,5","D",IF(H19="±1%","F",IF(H19="±2%","G",IF(H19="±5%","J",IF(H19="±10%","K",IF(H19="±20%","M","")))))))))</f>
+        <f t="shared" ref="R19" si="7">"C-"&amp;D19&amp;"-"&amp;G19&amp;"-"&amp;F19&amp;"-"&amp;E19&amp;" "&amp;IF(H19="±0,03","A",IF(H19="±0,1","B",IF(H19="±0,25","C",IF(H19="±0,5","D",IF(H19="±1%","F",IF(H19="±2%","G",IF(H19="±5%","J",IF(H19="±10%","K",IF(H19="±20%","M","")))))))))</f>
         <v xml:space="preserve">C-0603-NP0-250-2pF </v>
       </c>
       <c r="S19" s="5" t="str">
-        <f t="shared" ref="S19" si="9">R19</f>
+        <f t="shared" ref="S19" si="8">R19</f>
         <v xml:space="preserve">C-0603-NP0-250-2pF </v>
       </c>
     </row>
@@ -14689,7 +15238,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -19131,8 +19680,377 @@
         <v>R-0603-0R025 F</v>
       </c>
     </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="10" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F109" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I109" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J109" s="11" t="str">
+        <f t="shared" ref="J109:J110" si="12">"R"&amp;D109</f>
+        <v>R0402</v>
+      </c>
+      <c r="K109" s="11" t="str">
+        <f>"R-"&amp;D109&amp;"-"&amp;E109&amp;" "&amp;IF(F109="±0,03","A",IF(F109="±0,1","B",IF(F109="±0,25","C",IF(F109="±0,5","D",IF(F109="±1%","F",IF(F109="±2%","G",IF(F109="±5%","J",IF(F109="±10%","K",IF(F109="±20%","M","")))))))))</f>
+        <v>R-0402-806R F</v>
+      </c>
+      <c r="L109" s="10" t="str">
+        <f>K109</f>
+        <v>R-0402-806R F</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" s="10" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F110" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J110" s="11" t="str">
+        <f t="shared" si="12"/>
+        <v>R0402</v>
+      </c>
+      <c r="K110" s="11" t="str">
+        <f t="shared" ref="K110" si="13">"R-"&amp;D110&amp;"-"&amp;E110&amp;" "&amp;IF(F110="±0,03","A",IF(F110="±0,1","B",IF(F110="±0,25","C",IF(F110="±0,5","D",IF(F110="±1%","F",IF(F110="±2%","G",IF(F110="±5%","J",IF(F110="±10%","K",IF(F110="±20%","M","")))))))))</f>
+        <v>R-0402-121K F</v>
+      </c>
+      <c r="L110" s="10" t="str">
+        <f t="shared" ref="L110" si="14">K110</f>
+        <v>R-0402-121K F</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" s="10" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F111" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J111" s="11" t="str">
+        <f t="shared" ref="J111" si="15">"R"&amp;D111</f>
+        <v>R0402</v>
+      </c>
+      <c r="K111" s="11" t="str">
+        <f t="shared" ref="K111" si="16">"R-"&amp;D111&amp;"-"&amp;E111&amp;" "&amp;IF(F111="±0,03","A",IF(F111="±0,1","B",IF(F111="±0,25","C",IF(F111="±0,5","D",IF(F111="±1%","F",IF(F111="±2%","G",IF(F111="±5%","J",IF(F111="±10%","K",IF(F111="±20%","M","")))))))))</f>
+        <v>R-0402-365K F</v>
+      </c>
+      <c r="L111" s="10" t="str">
+        <f t="shared" ref="L111" si="17">K111</f>
+        <v>R-0402-365K F</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F112" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J112" s="11" t="str">
+        <f t="shared" ref="J112:J114" si="18">"R"&amp;D112</f>
+        <v>R0402</v>
+      </c>
+      <c r="K112" s="11" t="str">
+        <f t="shared" ref="K112:K114" si="19">"R-"&amp;D112&amp;"-"&amp;E112&amp;" "&amp;IF(F112="±0,03","A",IF(F112="±0,1","B",IF(F112="±0,25","C",IF(F112="±0,5","D",IF(F112="±1%","F",IF(F112="±2%","G",IF(F112="±5%","J",IF(F112="±10%","K",IF(F112="±20%","M","")))))))))</f>
+        <v>R-0402-23K2 F</v>
+      </c>
+      <c r="L112" s="10" t="str">
+        <f t="shared" ref="L112:L114" si="20">K112</f>
+        <v>R-0402-23K2 F</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" s="48" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D113" s="48" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E113" s="48" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F113" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I113" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J113" s="11" t="str">
+        <f t="shared" si="18"/>
+        <v>R1210</v>
+      </c>
+      <c r="K113" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v>R-1210-150R F</v>
+      </c>
+      <c r="L113" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v>R-1210-150R F</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" s="48" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B114" s="48" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="48" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F114" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H114" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I114" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J114" s="11" t="str">
+        <f t="shared" si="18"/>
+        <v>R0402</v>
+      </c>
+      <c r="K114" s="11" t="str">
+        <f t="shared" si="19"/>
+        <v>R-0402-309K F</v>
+      </c>
+      <c r="L114" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v>R-0402-309K F</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" s="48" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B115" s="48" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="48" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F115" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I115" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J115" s="11" t="str">
+        <f t="shared" ref="J115" si="21">"R"&amp;D115</f>
+        <v>R0402</v>
+      </c>
+      <c r="K115" s="11" t="str">
+        <f t="shared" ref="K115" si="22">"R-"&amp;D115&amp;"-"&amp;E115&amp;" "&amp;IF(F115="±0,03","A",IF(F115="±0,1","B",IF(F115="±0,25","C",IF(F115="±0,5","D",IF(F115="±1%","F",IF(F115="±2%","G",IF(F115="±5%","J",IF(F115="±10%","K",IF(F115="±20%","M","")))))))))</f>
+        <v>R-0402-22K F</v>
+      </c>
+      <c r="L115" s="10" t="str">
+        <f t="shared" ref="L115" si="23">K115</f>
+        <v>R-0402-22K F</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" s="48" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B116" s="48" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="48" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F116" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J116" s="11" t="str">
+        <f t="shared" ref="J116:J117" si="24">"R"&amp;D116</f>
+        <v>R0402</v>
+      </c>
+      <c r="K116" s="11" t="str">
+        <f t="shared" ref="K116:K117" si="25">"R-"&amp;D116&amp;"-"&amp;E116&amp;" "&amp;IF(F116="±0,03","A",IF(F116="±0,1","B",IF(F116="±0,25","C",IF(F116="±0,5","D",IF(F116="±1%","F",IF(F116="±2%","G",IF(F116="±5%","J",IF(F116="±10%","K",IF(F116="±20%","M","")))))))))</f>
+        <v>R-0402-28K F</v>
+      </c>
+      <c r="L116" s="10" t="str">
+        <f t="shared" ref="L116:L117" si="26">K116</f>
+        <v>R-0402-28K F</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" s="48" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E117" s="48" t="s">
+        <v>1602</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I117" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J117" s="11" t="str">
+        <f t="shared" si="24"/>
+        <v>R0805</v>
+      </c>
+      <c r="K117" s="11" t="str">
+        <f t="shared" si="25"/>
+        <v>R-0805-10R F</v>
+      </c>
+      <c r="L117" s="10" t="str">
+        <f t="shared" si="26"/>
+        <v>R-0805-10R F</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J108">
+  <conditionalFormatting sqref="J2:J117">
     <cfRule type="containsBlanks" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19144,7 +20062,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" style="10" customWidth="1"/>
@@ -19236,7 +20154,7 @@
         <v>590</v>
       </c>
       <c r="K2" s="48" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="L2" s="11" t="str">
         <f t="shared" ref="L2:L14" si="0">IF(I2="IND","L-",IF(I2="Ferrite","F-",""))&amp;A2</f>
@@ -19279,7 +20197,7 @@
         <v>590</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="L3" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19322,7 +20240,7 @@
         <v>590</v>
       </c>
       <c r="K4" s="48" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="L4" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19365,7 +20283,7 @@
         <v>590</v>
       </c>
       <c r="K5" s="48" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="L5" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19408,7 +20326,7 @@
         <v>590</v>
       </c>
       <c r="K6" s="48" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="L6" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19451,7 +20369,7 @@
         <v>590</v>
       </c>
       <c r="K7" s="48" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="L7" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19494,7 +20412,7 @@
         <v>590</v>
       </c>
       <c r="K8" s="48" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="L8" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19537,7 +20455,7 @@
         <v>590</v>
       </c>
       <c r="K9" s="48" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="L9" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19580,7 +20498,7 @@
         <v>590</v>
       </c>
       <c r="K10" s="48" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="L10" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19623,7 +20541,7 @@
         <v>590</v>
       </c>
       <c r="K11" s="48" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="L11" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19666,7 +20584,7 @@
         <v>590</v>
       </c>
       <c r="K12" s="48" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="L12" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19709,7 +20627,7 @@
         <v>590</v>
       </c>
       <c r="K13" s="48" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="L13" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19752,7 +20670,7 @@
         <v>590</v>
       </c>
       <c r="K14" s="48" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="L14" s="11" t="str">
         <f t="shared" si="0"/>
@@ -19795,7 +20713,7 @@
         <v>590</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="L15" s="11" t="str">
         <f t="shared" ref="L15:L18" si="2">IF(I15="IND","L-",IF(I15="Ferrite","F-",""))&amp;A15</f>
@@ -19838,7 +20756,7 @@
         <v>590</v>
       </c>
       <c r="K16" s="48" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="L16" s="11" t="str">
         <f t="shared" si="2"/>
@@ -19851,25 +20769,25 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="48" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>1501</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>1502</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>584</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="F17" t="s">
         <v>586</v>
       </c>
       <c r="G17" s="48" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>588</v>
@@ -19881,7 +20799,7 @@
         <v>590</v>
       </c>
       <c r="K17" s="48" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="L17" s="11" t="str">
         <f t="shared" si="2"/>
@@ -19894,10 +20812,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>604</v>
@@ -19906,13 +20824,13 @@
         <v>90</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F18" t="s">
         <v>586</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>588</v>
@@ -19924,7 +20842,7 @@
         <v>590</v>
       </c>
       <c r="K18" s="48" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="L18" s="11" t="str">
         <f t="shared" si="2"/>
@@ -19937,10 +20855,10 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>604</v>
@@ -19949,13 +20867,13 @@
         <v>90</v>
       </c>
       <c r="E19" s="48" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="F19" t="s">
         <v>586</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>588</v>
@@ -19967,23 +20885,23 @@
         <v>590</v>
       </c>
       <c r="K19" s="48" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="L19" s="11" t="str">
-        <f t="shared" ref="L19:L21" si="4">IF(I19="IND","L-",IF(I19="Ferrite","F-",""))&amp;A19</f>
+        <f t="shared" ref="L19:L22" si="4">IF(I19="IND","L-",IF(I19="Ferrite","F-",""))&amp;A19</f>
         <v>L-LQW18AS12NG00D</v>
       </c>
       <c r="M19" s="11" t="str">
-        <f t="shared" ref="M19:M21" si="5">L19</f>
+        <f t="shared" ref="M19:M22" si="5">L19</f>
         <v>L-LQW18AS12NG00D</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="48" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>584</v>
@@ -19992,13 +20910,13 @@
         <v>90</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="F20" t="s">
         <v>586</v>
       </c>
       <c r="G20" s="48" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>588</v>
@@ -20010,7 +20928,7 @@
         <v>590</v>
       </c>
       <c r="K20" s="48" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="L20" s="11" t="str">
         <f t="shared" si="4"/>
@@ -20023,10 +20941,10 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>584</v>
@@ -20035,13 +20953,13 @@
         <v>90</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F21" t="s">
         <v>586</v>
       </c>
       <c r="G21" s="48" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>588</v>
@@ -20053,7 +20971,7 @@
         <v>590</v>
       </c>
       <c r="K21" s="48" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="L21" s="11" t="str">
         <f t="shared" si="4"/>
@@ -20062,6 +20980,49 @@
       <c r="M21" s="11" t="str">
         <f t="shared" si="5"/>
         <v>L-0603HC-15NXJLW</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="48" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F22" t="s">
+        <v>586</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>1606</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="K22" s="48" t="s">
+        <v>1607</v>
+      </c>
+      <c r="L22" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>L-0603LS-102XJ</v>
+      </c>
+      <c r="M22" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>L-0603LS-102XJ</v>
       </c>
     </row>
   </sheetData>
@@ -20078,7 +21039,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="2" customWidth="1"/>
@@ -20156,11 +21117,11 @@
         <v>647</v>
       </c>
       <c r="J2" s="11" t="str">
-        <f t="shared" ref="J2:J16" si="0">IF(G2="IND","L-",IF(G2="Ferrite","F-",""))&amp;A2</f>
+        <f t="shared" ref="J2:J17" si="0">IF(G2="IND","L-",IF(G2="Ferrite","F-",""))&amp;A2</f>
         <v>L-74477020</v>
       </c>
       <c r="K2" s="11" t="str">
-        <f t="shared" ref="K2:K16" si="1">J2</f>
+        <f t="shared" ref="K2:K17" si="1">J2</f>
         <v>L-74477020</v>
       </c>
     </row>
@@ -20604,19 +21565,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="44" t="s">
         <v>1487</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="E15" s="44" t="s">
         <v>1488</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>1489</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>588</v>
@@ -20638,19 +21599,19 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B16" s="44" t="s">
         <v>1492</v>
       </c>
-      <c r="B16" s="44" t="s">
-        <v>1493</v>
-      </c>
       <c r="C16" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D16" s="44" t="s">
         <v>1490</v>
       </c>
-      <c r="D16" s="44" t="s">
-        <v>1491</v>
-      </c>
       <c r="E16" s="44" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>588</v>
@@ -20670,8 +21631,42 @@
         <v>L-SPQ105-150M</v>
       </c>
     </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="J17" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>L-B82472G6223M000</v>
+      </c>
+      <c r="K17" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>L-B82472G6223M000</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="containsBlanks" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20890,7 +21885,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.125" style="2" customWidth="1"/>
@@ -20954,7 +21949,7 @@
         <v>159</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>160</v>
@@ -20997,7 +21992,7 @@
         <v>168</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>160</v>
@@ -21083,7 +22078,7 @@
         <v>176</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>160</v>
@@ -21126,7 +22121,7 @@
         <v>177</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>160</v>
@@ -21169,7 +22164,7 @@
         <v>180</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>160</v>
@@ -21210,7 +22205,7 @@
         <v>183</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>160</v>
@@ -21251,7 +22246,7 @@
         <v>187</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>160</v>
@@ -21294,7 +22289,7 @@
         <v>194</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>160</v>
@@ -21335,7 +22330,7 @@
         <v>1241</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>198</v>
@@ -21378,7 +22373,7 @@
         <v>203</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>198</v>
@@ -21421,7 +22416,7 @@
         <v>208</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>198</v>
@@ -21464,7 +22459,7 @@
         <v>212</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>198</v>
@@ -21507,7 +22502,7 @@
         <v>216</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>198</v>
@@ -21550,7 +22545,7 @@
         <v>219</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>160</v>
@@ -21593,7 +22588,7 @@
         <v>225</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>160</v>
@@ -21636,7 +22631,7 @@
         <v>231</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>160</v>
@@ -21677,7 +22672,7 @@
         <v>235</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>160</v>
@@ -21720,7 +22715,7 @@
         <v>240</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>160</v>
@@ -21794,7 +22789,7 @@
         <v>SGM2208XTDF12G/TR</v>
       </c>
       <c r="M21" s="5" t="str">
-        <f t="shared" ref="M21:M38" si="2">L21</f>
+        <f t="shared" ref="M21:M39" si="2">L21</f>
         <v>SGM2208XTDF12G/TR</v>
       </c>
     </row>
@@ -21803,7 +22798,7 @@
         <v>252</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>198</v>
@@ -21846,7 +22841,7 @@
         <v>256</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>198</v>
@@ -21889,7 +22884,7 @@
         <v>257</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>198</v>
@@ -21932,7 +22927,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>198</v>
@@ -21973,7 +22968,7 @@
         <v>266</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>198</v>
@@ -22016,7 +23011,7 @@
         <v>272</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>198</v>
@@ -22059,7 +23054,7 @@
         <v>278</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>198</v>
@@ -22102,7 +23097,7 @@
         <v>283</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>198</v>
@@ -22145,7 +23140,7 @@
         <v>288</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>160</v>
@@ -22188,7 +23183,7 @@
         <v>1242</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>160</v>
@@ -22230,7 +23225,7 @@
         <v>1271</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>160</v>
@@ -22273,7 +23268,7 @@
         <v>1276</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>160</v>
@@ -22316,7 +23311,7 @@
         <v>1285</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>160</v>
@@ -22357,7 +23352,7 @@
         <v>1358</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>160</v>
@@ -22485,8 +23480,8 @@
       <c r="A38" s="33" t="s">
         <v>1383</v>
       </c>
-      <c r="B38" s="33" t="s">
-        <v>1384</v>
+      <c r="B38" s="44" t="s">
+        <v>1567</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>198</v>
@@ -22495,10 +23490,10 @@
         <v>1354</v>
       </c>
       <c r="E38" s="33" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F38" s="33" t="s">
         <v>1385</v>
-      </c>
-      <c r="F38" s="33" t="s">
-        <v>1386</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>190</v>
@@ -22522,6 +23517,92 @@
       <c r="M38" s="5" t="str">
         <f t="shared" si="2"/>
         <v>LM51581RTER</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>1553</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K39" s="44" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L39" s="5" t="str">
+        <f>LibraryTable3[[#This Row],[Part Number]]</f>
+        <v>TPS7A4001DGNR</v>
+      </c>
+      <c r="M39" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>TPS7A4001DGNR</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="44" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I40" s="44" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K40" s="33" t="s">
+        <v>1354</v>
+      </c>
+      <c r="L40" s="5" t="str">
+        <f>LibraryTable3[[#This Row],[Part Number]]</f>
+        <v>LM5158RTER</v>
+      </c>
+      <c r="M40" s="5" t="str">
+        <f t="shared" ref="M40" si="3">L40</f>
+        <v>LM5158RTER</v>
       </c>
     </row>
   </sheetData>
@@ -22540,11 +23621,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="41" style="2" customWidth="1"/>
+    <col min="2" max="2" width="51.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.125" style="2" customWidth="1"/>
@@ -22827,11 +23908,11 @@
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="2" t="str">
-        <f t="shared" ref="J8:J13" si="2">A8</f>
+        <f t="shared" ref="J8:J15" si="2">A8</f>
         <v>ASGTX-C-120.00MHZ-1</v>
       </c>
       <c r="K8" s="2" t="str">
-        <f t="shared" ref="K8:K13" si="3">J8</f>
+        <f t="shared" ref="K8:K15" si="3">J8</f>
         <v>ASGTX-C-120.00MHZ-1</v>
       </c>
     </row>
@@ -23015,6 +24096,80 @@
       <c r="K13" s="5" t="str">
         <f t="shared" si="3"/>
         <v>OPA4197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>1558</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="J14" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>OPA197IDBV</v>
+      </c>
+      <c r="K14" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>OPA197IDBV</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>1586</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="J15" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>TPS3711DDC</v>
+      </c>
+      <c r="K15" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>TPS3711DDC</v>
       </c>
     </row>
   </sheetData>
